--- a/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10726"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB35EA3-9C22-FB45-873E-75EEB1A08AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5557A045-0F2D-F149-8CD2-AB4A31DBCC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11720" yWindow="3840" windowWidth="35840" windowHeight="20900" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="AssociatedElements" sheetId="2" r:id="rId3"/>
     <sheet name="Lists" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="348">
   <si>
     <t>Description</t>
   </si>
@@ -992,9 +992,6 @@
     <t>pull_speed</t>
   </si>
   <si>
-    <t>pull speed</t>
-  </si>
-  <si>
     <t>Lift rate of the monitor while grouting</t>
   </si>
   <si>
@@ -1077,13 +1074,19 @@
   </si>
   <si>
     <t>ancestor::diggs:ContinuousGrouting</t>
+  </si>
+  <si>
+    <t>pull speed|withdrawal rate</t>
+  </si>
+  <si>
+    <t>ancestor::diggs:constructionActivity//diggs:RIInstallationRecord</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1187,6 +1190,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1299,7 +1308,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1345,16 +1354,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1370,77 +1384,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1579,6 +1522,77 @@
       </font>
       <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1593,51 +1607,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H37" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H37" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="7">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B872,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:E45" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:E45" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C2">
-    <sortCondition ref="C1:C2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:E48" totalsRowShown="0" headerRowDxfId="21">
+  <autoFilter ref="A1:E48" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E45">
+    <sortCondition ref="B1:B45"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="20">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1843,1,FALSE)),"Not listed","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ConditionalElement" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ConditionalElement" dataDxfId="17"/>
     <tableColumn id="5" xr3:uid="{70DA9ABB-01EE-9C4D-9F26-0BFC80A8CC6E}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1962,7 +1976,7 @@
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>233</v>
@@ -1971,7 +1985,7 @@
         <v>234</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -2630,10 +2644,10 @@
         <v>317</v>
       </c>
       <c r="C29" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>318</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>319</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>1</v>
@@ -2649,13 +2663,13 @@
         <v/>
       </c>
       <c r="B30" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="D30" s="17" t="s">
         <v>321</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>322</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>1</v>
@@ -2671,13 +2685,13 @@
         <v/>
       </c>
       <c r="B31" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="D31" s="17" t="s">
         <v>324</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>325</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>1</v>
@@ -2693,19 +2707,19 @@
         <v/>
       </c>
       <c r="B32" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="D32" s="17" t="s">
         <v>327</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>328</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G32" s="11"/>
     </row>
@@ -2715,13 +2729,13 @@
         <v/>
       </c>
       <c r="B33" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="D33" s="17" t="s">
         <v>331</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>332</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>180</v>
@@ -2737,13 +2751,13 @@
         <v/>
       </c>
       <c r="B34" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="D34" s="17" t="s">
         <v>334</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>335</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>1</v>
@@ -2759,13 +2773,13 @@
         <v/>
       </c>
       <c r="B35" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="D35" s="17" t="s">
         <v>336</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>337</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>1</v>
@@ -2781,13 +2795,13 @@
         <v/>
       </c>
       <c r="B36" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="D36" s="18" t="s">
         <v>338</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>339</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>1</v>
@@ -2808,13 +2822,13 @@
       <c r="C37" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="E37" s="22" t="s">
+      <c r="D37" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="E37" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="21" t="s">
         <v>25</v>
       </c>
       <c r="G37" s="11"/>
@@ -2843,7 +2857,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
@@ -2866,7 +2880,7 @@
         <v>226</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -2877,11 +2891,11 @@
       <c r="B2" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -2892,11 +2906,11 @@
       <c r="B3" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -2907,11 +2921,11 @@
       <c r="B4" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>344</v>
+      <c r="C4" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -2922,11 +2936,11 @@
       <c r="B5" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>344</v>
+      <c r="C5" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -2937,11 +2951,11 @@
       <c r="B6" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>344</v>
+      <c r="C6" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2952,11 +2966,11 @@
       <c r="B7" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>344</v>
+      <c r="C7" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -2967,11 +2981,11 @@
       <c r="B8" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -2982,11 +2996,11 @@
       <c r="B9" t="s">
         <v>255</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -2997,11 +3011,11 @@
       <c r="B10" t="s">
         <v>255</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>344</v>
+      <c r="C10" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -3012,11 +3026,11 @@
       <c r="B11" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>344</v>
+      <c r="C11" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -3027,11 +3041,11 @@
       <c r="B12" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>344</v>
+      <c r="C12" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -3042,11 +3056,11 @@
       <c r="B13" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>344</v>
+      <c r="C13" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -3057,11 +3071,11 @@
       <c r="B14" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>344</v>
+      <c r="C14" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -3072,11 +3086,11 @@
       <c r="B15" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>344</v>
+      <c r="C15" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -3087,11 +3101,11 @@
       <c r="B16" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>344</v>
+      <c r="C16" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -3102,11 +3116,11 @@
       <c r="B17" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C17" s="24" t="s">
-        <v>344</v>
+      <c r="C17" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -3117,11 +3131,11 @@
       <c r="B18" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3132,11 +3146,11 @@
       <c r="B19" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>344</v>
+      <c r="C19" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -3147,11 +3161,11 @@
       <c r="B20" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -3162,11 +3176,11 @@
       <c r="B21" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>344</v>
+      <c r="C21" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -3177,11 +3191,11 @@
       <c r="B22" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -3192,11 +3206,11 @@
       <c r="B23" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>344</v>
+      <c r="C23" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -3207,11 +3221,11 @@
       <c r="B24" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -3222,11 +3236,11 @@
       <c r="B25" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="C25" s="24" t="s">
-        <v>344</v>
+      <c r="C25" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -3237,11 +3251,11 @@
       <c r="B26" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="C26" s="24" t="s">
-        <v>344</v>
+      <c r="C26" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -3252,11 +3266,11 @@
       <c r="B27" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="C27" s="24" t="s">
-        <v>344</v>
+      <c r="C27" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -3267,11 +3281,11 @@
       <c r="B28" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -3282,11 +3296,11 @@
       <c r="B29" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D29" t="s">
         <v>344</v>
-      </c>
-      <c r="D29" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -3297,11 +3311,11 @@
       <c r="B30" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="C30" s="24" t="s">
-        <v>344</v>
+      <c r="C30" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -3312,11 +3326,11 @@
       <c r="B31" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>344</v>
+      <c r="C31" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -3327,11 +3341,11 @@
       <c r="B32" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" t="s">
         <v>344</v>
-      </c>
-      <c r="D32" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -3342,11 +3356,11 @@
       <c r="B33" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D33" t="s">
         <v>344</v>
-      </c>
-      <c r="D33" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -3357,11 +3371,11 @@
       <c r="B34" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>344</v>
+      <c r="C34" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -3370,13 +3384,13 @@
         <v/>
       </c>
       <c r="B35" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>344</v>
+        <v>319</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -3385,13 +3399,13 @@
         <v/>
       </c>
       <c r="B36" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>344</v>
+        <v>322</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -3400,13 +3414,13 @@
         <v/>
       </c>
       <c r="B37" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>344</v>
+        <v>325</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -3415,13 +3429,13 @@
         <v/>
       </c>
       <c r="B38" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>344</v>
+        <v>329</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -3430,13 +3444,13 @@
         <v/>
       </c>
       <c r="B39" t="s">
-        <v>330</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>344</v>
+        <v>329</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -3445,13 +3459,13 @@
         <v/>
       </c>
       <c r="B40" t="s">
-        <v>333</v>
-      </c>
-      <c r="C40" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D40" s="20" t="s">
         <v>344</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -3460,13 +3474,13 @@
         <v/>
       </c>
       <c r="B41" t="s">
-        <v>333</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>344</v>
+        <v>332</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -3475,13 +3489,13 @@
         <v/>
       </c>
       <c r="B42" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>344</v>
+        <v>335</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -3490,14 +3504,15 @@
         <v/>
       </c>
       <c r="B43" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>344</v>
+        <v>25</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>346</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="E43" s="23"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="str">
@@ -3507,13 +3522,13 @@
       <c r="B44" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E44" s="21"/>
+      <c r="E44" s="24"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="str">
@@ -3521,13 +3536,58 @@
         <v/>
       </c>
       <c r="B45" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>344</v>
+        <v>337</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="25" t="str">
+        <f>IF(ISNA(VLOOKUP(B46,Definitions!B$2:B$1843,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="25" t="str">
+        <f>IF(ISNA(VLOOKUP(B47,Definitions!B$2:B$1843,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="25" t="str">
+        <f>IF(ISNA(VLOOKUP(B48,Definitions!B$2:B$1843,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The ratio of actual to theoretical grout or concrete volume placed at a given depth during installation, expressed as a percentage - the depth-indexed counterpart to a Menard CMC installation record (GIW p.42). A GENUINE COVERAGE QUANTITY, NOT A REPEAT OF A COLUMN-LEVEL COMPUTATION: RigidInclusionType already carries theoreticalGroutVolume and placedGroutVolume, so the whole-column overconsumption ratio is derivable from those two without this entry - but that derived ratio cannot say WHERE along the column the overconsumption occurred, which is what a Menard-style rig log actually records and what a reviewer needs to see a void, a soft layer or a loss zone. Carry both: the column-level total on RigidInclusionType is the separate, out-of-scope-for-this-entry summary; this entry is the per-reading value that makes the profile against depth expressible at all.</t>
+          <t>The ratio of actual to theoretical grout or concrete volume placed at a given depth during installation, expressed as a percentage - the depth-indexed counterpart to a Menard CMC installation record (GIW p.42). A GENUINE COVERAGE QUANTITY, NOT A REPEAT OF A COLUMN-LEVEL COMPUTATION: RIColumnType already carries theoreticalGroutVolume and placedGroutVolume, so the whole-column overconsumption ratio is derivable from those two without this entry - but that derived ratio cannot say WHERE along the column the overconsumption occurred, which is what a Menard-style rig log actually records and what a reviewer needs to see a void, a soft layer or a loss zone. Carry both: the column-level total on RIColumnType is the separate, out-of-scope-for-this-entry summary; this entry is the per-reading value that makes the profile against depth expressible at all.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">

--- a/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
@@ -991,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="16.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -2226,6 +2226,60 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>grout_level</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>grout level</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>The elevation or depth of the grout surface within the column bore or annulus at a given reading, used to detect an in-progress drop in grout level - a sign the column is losing grout into the surrounding ground and is at risk of an 'uncovered column' condition (V2 Installation row 31). Where a drop triggers a corrective action, that outcome is recorded separately as diggs:RIConstructionActivityType/groutLevelCorrectiveAction; this entry carries only the level reading itself.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>grout_return_volume</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Grout return (wet-squeeze) volume</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>The volume of grout or slurry returning to the surface during installation - a 'wet squeeze' - distinct from volume_overconsumption (excess grout pumped versus theoretical, in-bore and depth-indexed): this is fluid actually emerging at the surface, and is often observed at an already-installed neighbouring column rather than the one currently being drilled or grouted. Where that is the case, record this reading against whichever column's installationRecord the observer is logging against, and use remark to note which column the return was actually attributed to if it differs (V2 Installation row 32).</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2241,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" style="25" min="1" max="1"/>
@@ -3384,6 +3438,40 @@
         </is>
       </c>
       <c r="D56" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:constructionActivity//diggs:RIInstallationRecord</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>grout_level</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:constructionActivity//diggs:RIInstallationRecord</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>grout_return_volume</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>ancestor::diggs:constructionActivity//diggs:RIInstallationRecord</t>
         </is>

--- a/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grout_inj_properties.xlsx
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The elevation or depth of the grout surface within the column bore or annulus at a given reading, used to detect an in-progress drop in grout level - a sign the column is losing grout into the surrounding ground and is at risk of an 'uncovered column' condition (V2 Installation row 31). Where a drop triggers a corrective action, that outcome is recorded separately as diggs:RIConstructionActivityType/groutLevelCorrectiveAction; this entry carries only the level reading itself.</t>
+          <t>The elevation or depth of the grout surface within the column bore or annulus at a given reading, used to detect an in-progress drop in grout level - a sign the column is losing grout into the surrounding ground and is at risk of an 'uncovered column' condition (V2 Installation row 31). Where a drop triggers a corrective action, that outcome is recorded separately as diggs:RIColumnConstructionType/groutLevelCorrectiveAction; this entry carries only the level reading itself.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
